--- a/artfynd/S 5521-2022 artfynd.xlsx
+++ b/artfynd/S 5521-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY102"/>
+  <dimension ref="A1:AZ102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100310828</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91866296</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99902542</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101850678</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1219,6 +1244,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/177655</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1335,6 +1365,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/182467</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1447,6 +1482,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73077663</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1559,6 +1599,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73077684</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1671,6 +1716,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73077696</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1783,6 +1833,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73077708</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1897,6 +1952,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103352292</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2006,6 +2066,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120084145</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2131,6 +2196,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/261617</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2246,6 +2316,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100705329</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2361,6 +2436,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101850702</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2472,6 +2552,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/334342</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2588,6 +2673,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/338211</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2697,6 +2787,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82839931</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2798,6 +2893,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91866300</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2913,6 +3013,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99673553</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3024,6 +3129,11 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69549702</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3139,6 +3249,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103223258</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3255,6 +3370,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101850667</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3375,6 +3495,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103223307</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3489,6 +3614,11 @@
       <c r="AY26" t="inlineStr">
         <is>
           <t>Svampar i Roslagen</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118335105</t>
         </is>
       </c>
     </row>
@@ -3592,6 +3722,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82839950</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3701,6 +3836,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90060580</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3820,6 +3960,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99585794</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3935,6 +4080,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100705341</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4036,6 +4186,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91866347</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4151,6 +4306,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100540738</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4266,6 +4426,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100310824</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4381,6 +4546,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100705332</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4496,6 +4666,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101850672</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4611,6 +4786,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99673536</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4712,6 +4892,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122363337</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4831,6 +5016,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123359489</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4950,6 +5140,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100213810</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5069,6 +5264,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123359277</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5192,6 +5392,11 @@
       <c r="AY41" t="inlineStr">
         <is>
           <t>Fladdermöss-Inventering Norrtälje</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71388189</t>
         </is>
       </c>
     </row>
@@ -5311,6 +5516,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101101245</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5436,6 +5646,11 @@
           <t>Fladdermöss-Inventering Norrtälje</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71388179</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5561,6 +5776,11 @@
           <t>Fladdermöss-Inventering Norrtälje</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71388177</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5681,6 +5901,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54997568</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5797,6 +6022,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60067060</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5914,6 +6144,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/12987878</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6031,6 +6266,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/12987890</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6155,6 +6395,11 @@
           <t>Svenska entomologmötet i Norrtälje, Uppland 26 - 28 juni 2026</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134700008</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6274,6 +6519,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100482496</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6389,6 +6639,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96897994</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6506,6 +6761,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/12987917</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6637,6 +6897,11 @@
       <c r="AY53" t="inlineStr">
         <is>
           <t>Svenska entomologmötet i Norrtälje, Uppland 26 - 28 juni 2026</t>
+        </is>
+      </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134777000</t>
         </is>
       </c>
     </row>
@@ -6754,6 +7019,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101099374</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6869,6 +7139,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101099371</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6984,6 +7259,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100259139</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7103,6 +7383,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123359553</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7218,6 +7503,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101099390</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7333,6 +7623,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101850718</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7452,6 +7747,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123359526</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7571,6 +7871,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100676682</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7687,6 +7992,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134700001</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7802,6 +8112,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101099388</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7921,6 +8236,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100482491</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8036,6 +8356,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96897993</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8159,6 +8484,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100258571</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8264,6 +8594,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121950630</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8383,6 +8718,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123359578</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8498,6 +8838,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101099393</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8609,6 +8954,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123359531</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8724,6 +9074,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123359444</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8841,6 +9196,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/12987817</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8960,6 +9320,11 @@
           <t>Svenska entomologmötet i Norrtälje, Uppland 26 - 28 juni 2026</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134792103</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9085,6 +9450,11 @@
           <t>Fladdermöss-Inventering Norrtälje</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71388187</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9210,6 +9580,11 @@
           <t>Fladdermöss-Inventering Norrtälje</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71388176</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9335,6 +9710,11 @@
           <t>Fladdermöss-Inventering Norrtälje</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71388171</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9460,6 +9840,11 @@
           <t>Fladdermöss-Inventering Norrtälje</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71388190</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9574,6 +9959,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62867864</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9676,6 +10066,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59788643</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9783,6 +10178,11 @@
           <t>Svenska entomologmötet i Norrtälje, Uppland 26 - 28 juni 2026</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134738214</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9889,6 +10289,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59788573</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10004,6 +10409,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110464270</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10119,6 +10529,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110464266</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10234,6 +10649,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110464234</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10344,6 +10764,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83429726</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10459,6 +10884,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110465468</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10569,6 +10999,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83431395</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10684,6 +11119,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110512014</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10799,6 +11239,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110512011</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10909,6 +11354,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83433515</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -11024,6 +11474,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110467412</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11134,6 +11589,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83434973</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11249,6 +11709,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110467416</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11364,6 +11829,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110467428</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11479,6 +11949,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110467409</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11594,6 +12069,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110467423</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11709,6 +12189,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110512016</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11822,6 +12307,11 @@
       <c r="AY98" t="inlineStr">
         <is>
           <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110512018</t>
         </is>
       </c>
     </row>
@@ -11926,6 +12416,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77423734</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -12034,6 +12529,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109247157</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -12145,6 +12645,11 @@
           <t>Upplands Flora 2010</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69549718</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12252,8 +12757,116 @@
           <t>Svampar i Roslagen</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118335499</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 5521-2022 artfynd.xlsx
+++ b/artfynd/S 5521-2022 artfynd.xlsx
@@ -3624,51 +3624,48 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>82839950</v>
+        <v>118335499</v>
       </c>
       <c r="B27" t="n">
-        <v>91867</v>
+        <v>89206</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5445</v>
+        <v>4393</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Papegojvaxing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Gliophorus psittacinus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) Herink</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Mellingeholm, Limmaren, Upl</t>
+          <t>Mellingeholm, Mellingeholm, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>708195</v>
+        <v>708181</v>
       </c>
       <c r="R27" t="n">
-        <v>6627382</v>
+        <v>6627281</v>
       </c>
       <c r="S27" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3692,12 +3689,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2020-03-15</t>
+          <t>2023-07-28</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2020-03-15</t>
+          <t>2023-07-28</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Kollekt 4155.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3706,31 +3718,34 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Micael Söderman</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Micael Söderman</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82839950</t>
+          <t>https://artportalen.se/Sighting/118335499</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>90060580</v>
+        <v>82839950</v>
       </c>
       <c r="B28" t="n">
         <v>91867</v>
@@ -3758,31 +3773,23 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mellingeholmsparken, Limmaren, Upl</t>
+          <t>Mellingeholm, Limmaren, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>708115</v>
+        <v>708195</v>
       </c>
       <c r="R28" t="n">
-        <v>6627367</v>
+        <v>6627382</v>
       </c>
       <c r="S28" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3806,12 +3813,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2021-01-06</t>
+          <t>2020-03-15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2021-01-06</t>
+          <t>2020-03-15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3838,13 +3845,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/90060580</t>
+          <t>https://artportalen.se/Sighting/82839950</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>99585794</v>
+        <v>90060580</v>
       </c>
       <c r="B29" t="n">
         <v>91867</v>
@@ -3874,7 +3881,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3886,17 +3893,17 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Melinge holm park, Upl</t>
+          <t>Mellingeholmsparken, Limmaren, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>708079</v>
+        <v>708115</v>
       </c>
       <c r="R29" t="n">
-        <v>6627430</v>
+        <v>6627367</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3920,22 +3927,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>07:30</t>
+          <t>2021-01-06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2021-01-06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3951,24 +3948,24 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Lukas Stenbäck</t>
+          <t>Micael Söderman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Lukas Stenbäck</t>
+          <t>Micael Söderman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99585794</t>
+          <t>https://artportalen.se/Sighting/90060580</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>100705341</v>
+        <v>99585794</v>
       </c>
       <c r="B30" t="n">
         <v>91867</v>
@@ -3998,25 +3995,29 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Melinge holm, Upl</t>
+          <t>Melinge holm park, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>708050</v>
+        <v>708079</v>
       </c>
       <c r="R30" t="n">
-        <v>6627385</v>
+        <v>6627430</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4040,22 +4041,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2022-05-10</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2022-05-10</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4082,57 +4083,61 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100705341</t>
+          <t>https://artportalen.se/Sighting/99585794</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>91866347</v>
+        <v>100705341</v>
       </c>
       <c r="B31" t="n">
-        <v>78728</v>
+        <v>91867</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6436</v>
+        <v>5445</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gulpudrad spiklav</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Calicium adspersum</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Pers.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mellingeholms park, Upl</t>
+          <t>Melinge holm, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>708146</v>
+        <v>708050</v>
       </c>
       <c r="R31" t="n">
-        <v>6627365</v>
+        <v>6627385</v>
       </c>
       <c r="S31" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4156,12 +4161,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2021-03-25</t>
+          <t>2022-05-10</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2021-03-25</t>
+          <t>2022-05-10</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4177,27 +4192,27 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Lukas Stenbäck</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ossian Rydebjörk</t>
+          <t>Lukas Stenbäck</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/91866347</t>
+          <t>https://artportalen.se/Sighting/100705341</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>100540738</v>
+        <v>91866347</v>
       </c>
       <c r="B32" t="n">
-        <v>83290</v>
+        <v>78728</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4205,44 +4220,40 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6439</v>
+        <v>6436</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Gulpudrad spiklav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Calicium adspersum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Melinge holm park, Upl</t>
+          <t>Mellingeholms park, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>708079</v>
+        <v>708146</v>
       </c>
       <c r="R32" t="n">
-        <v>6627430</v>
+        <v>6627365</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4266,22 +4277,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>07:30</t>
+          <t>2021-03-25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2022-05-06</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>07:30</t>
+          <t>2021-03-25</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4297,27 +4298,27 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lukas Stenbäck</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lukas Stenbäck</t>
+          <t>Ossian Rydebjörk</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100540738</t>
+          <t>https://artportalen.se/Sighting/91866347</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>100310824</v>
+        <v>100540738</v>
       </c>
       <c r="B33" t="n">
-        <v>78685</v>
+        <v>83290</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4325,26 +4326,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6443</v>
+        <v>6439</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sotlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Acolium inquinans</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Sm.) A.Massal.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
@@ -4386,7 +4387,7 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2022-04-29</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
@@ -4396,12 +4397,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2022-04-29</t>
+          <t>2022-05-06</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4428,13 +4429,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100310824</t>
+          <t>https://artportalen.se/Sighting/100540738</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>100705332</v>
+        <v>100310824</v>
       </c>
       <c r="B34" t="n">
         <v>78685</v>
@@ -4464,7 +4465,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
@@ -4472,17 +4473,17 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Melinge holm, Upl</t>
+          <t>Melinge holm park, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>708050</v>
+        <v>708079</v>
       </c>
       <c r="R34" t="n">
-        <v>6627385</v>
+        <v>6627430</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4506,22 +4507,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2022-05-10</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2022-05-10</t>
+          <t>2022-04-29</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4548,13 +4549,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100705332</t>
+          <t>https://artportalen.se/Sighting/100310824</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>101850672</v>
+        <v>100705332</v>
       </c>
       <c r="B35" t="n">
         <v>78685</v>
@@ -4584,7 +4585,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
@@ -4592,17 +4593,17 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>M: Ekpark, Upl</t>
+          <t>Melinge holm, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>708142</v>
+        <v>708050</v>
       </c>
       <c r="R35" t="n">
-        <v>6627299</v>
+        <v>6627385</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4626,22 +4627,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2022-06-24</t>
+          <t>2022-05-10</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2022-06-24</t>
+          <t>2022-05-10</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4668,38 +4669,38 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101850672</t>
+          <t>https://artportalen.se/Sighting/100705332</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>99673536</v>
+        <v>101850672</v>
       </c>
       <c r="B36" t="n">
-        <v>83314</v>
+        <v>78685</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6471</v>
+        <v>6443</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gulvit blekspik</t>
+          <t>Sotlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sclerophora pallida</t>
+          <t>Acolium inquinans</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
+          <t>(Sm.) A.Massal.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4712,17 +4713,17 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Melinge holm park, Upl</t>
+          <t>M: Ekpark, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>708079</v>
+        <v>708142</v>
       </c>
       <c r="R36" t="n">
-        <v>6627430</v>
+        <v>6627299</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4746,22 +4747,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2022-04-05</t>
+          <t>2022-06-24</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2022-04-05</t>
+          <t>2022-06-24</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4788,13 +4789,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/99673536</t>
+          <t>https://artportalen.se/Sighting/101850672</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122363337</v>
+        <v>99673536</v>
       </c>
       <c r="B37" t="n">
         <v>83314</v>
@@ -4822,23 +4823,27 @@
           <t>(Pers.) Y.J.Jao &amp; Spooner</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Melingeholm ask, Upl</t>
+          <t>Melinge holm park, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>708179</v>
+        <v>708079</v>
       </c>
       <c r="R37" t="n">
-        <v>6627451</v>
+        <v>6627430</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4862,12 +4867,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2022-04-05</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-01-26</t>
+          <t>2022-04-05</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4894,63 +4909,54 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122363337</t>
+          <t>https://artportalen.se/Sighting/99673536</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123359489</v>
+        <v>122363337</v>
       </c>
       <c r="B38" t="n">
-        <v>56925</v>
+        <v>83314</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100045</v>
+        <v>6471</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Gulvit blekspik</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Sclerophora pallida</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Pers.) Y.J.Jao &amp; Spooner</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Melingeholm, Upl</t>
+          <t>Melingeholm ask, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>708142</v>
+        <v>708179</v>
       </c>
       <c r="R38" t="n">
-        <v>6627422</v>
+        <v>6627451</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4977,22 +4983,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>07:30</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>08:08</t>
+          <t>2025-01-26</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5001,6 +4997,7 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5018,33 +5015,33 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123359489</t>
+          <t>https://artportalen.se/Sighting/122363337</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>100213810</v>
+        <v>123359489</v>
       </c>
       <c r="B39" t="n">
-        <v>57966</v>
+        <v>56925</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100048</v>
+        <v>100045</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5054,30 +5051,30 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Melinge holm park, Upl</t>
+          <t>Melingeholm, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>708079</v>
+        <v>708142</v>
       </c>
       <c r="R39" t="n">
-        <v>6627430</v>
+        <v>6627422</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5101,22 +5098,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2022-04-25</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2022-04-25</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5142,13 +5139,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100213810</t>
+          <t>https://artportalen.se/Sighting/123359489</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123359277</v>
+        <v>100213810</v>
       </c>
       <c r="B40" t="n">
         <v>57966</v>
@@ -5185,23 +5182,23 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Melingeholm, Upl</t>
+          <t>Melinge holm park, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>708142</v>
+        <v>708079</v>
       </c>
       <c r="R40" t="n">
-        <v>6627422</v>
+        <v>6627430</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5225,22 +5222,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2022-04-25</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-03-19</t>
+          <t>2022-04-25</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:34</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5266,16 +5263,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123359277</t>
+          <t>https://artportalen.se/Sighting/100213810</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>71388189</v>
+        <v>123359277</v>
       </c>
       <c r="B41" t="n">
-        <v>56817</v>
+        <v>57966</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5283,21 +5280,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100051</v>
+        <v>100048</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sydfladdermus</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Eptesicus serotinus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5305,34 +5302,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>autobox</t>
-        </is>
-      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Inventeringslokal 30, Upl</t>
+          <t>Melingeholm, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>708263</v>
+        <v>708142</v>
       </c>
       <c r="R41" t="n">
-        <v>6627540</v>
+        <v>6627422</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5354,19 +5344,24 @@
           <t>Frötuna</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2017-07-04</t>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2017-07-05</t>
+          <t>2025-03-19</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>17:34</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5381,53 +5376,49 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Gesa von Hirschheydt</t>
+          <t>Lukas Stenbäck</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Gesa von Hirschheydt, Lara Millon, Johnny de Jong</t>
-        </is>
-      </c>
-      <c r="AY41" t="inlineStr">
-        <is>
-          <t>Fladdermöss-Inventering Norrtälje</t>
-        </is>
-      </c>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/71388189</t>
+          <t>https://artportalen.se/Sighting/123359277</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>101101245</v>
+        <v>71388189</v>
       </c>
       <c r="B42" t="n">
-        <v>56895</v>
+        <v>56817</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100088</v>
+        <v>100051</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Sydfladdermus</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Eptesicus serotinus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -5435,21 +5426,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Melinge holm park, Upl</t>
+          <t>Inventeringslokal 30, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>708079</v>
+        <v>708263</v>
       </c>
       <c r="R42" t="n">
-        <v>6627430</v>
+        <v>6627540</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5474,24 +5475,19 @@
           <t>Frötuna</t>
         </is>
       </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2017-07-04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2017-07-05</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5500,34 +5496,37 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lukas Stenbäck</t>
+          <t>Gesa von Hirschheydt</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lukas Stenbäck</t>
-        </is>
-      </c>
-      <c r="AY42" t="inlineStr"/>
+          <t>Gesa von Hirschheydt, Lara Millon, Johnny de Jong</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Fladdermöss-Inventering Norrtälje</t>
+        </is>
+      </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101101245</t>
+          <t>https://artportalen.se/Sighting/71388189</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>71388179</v>
+        <v>101101245</v>
       </c>
       <c r="B43" t="n">
-        <v>56830</v>
+        <v>56895</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5535,53 +5534,43 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100092</v>
+        <v>100088</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>autobox</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Inventeringslokal 30, Upl</t>
+          <t>Melinge holm park, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>708263</v>
+        <v>708079</v>
       </c>
       <c r="R43" t="n">
-        <v>6627540</v>
+        <v>6627430</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5606,19 +5595,24 @@
           <t>Frötuna</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2017-07-12</t>
+          <t>2022-05-24</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2017-07-13</t>
+          <t>2022-05-24</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5627,37 +5621,34 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Gesa von Hirschheydt</t>
+          <t>Lukas Stenbäck</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Gesa von Hirschheydt, Lara Millon, Johnny de Jong</t>
-        </is>
-      </c>
-      <c r="AY43" t="inlineStr">
-        <is>
-          <t>Fladdermöss-Inventering Norrtälje</t>
-        </is>
-      </c>
+          <t>Lukas Stenbäck</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/71388179</t>
+          <t>https://artportalen.se/Sighting/101101245</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>71388177</v>
+        <v>71388179</v>
       </c>
       <c r="B44" t="n">
-        <v>56833</v>
+        <v>56830</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5665,26 +5656,26 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>118</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5743,12 +5734,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2017-07-14</t>
+          <t>2017-07-12</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2017-07-15</t>
+          <t>2017-07-13</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5778,16 +5769,16 @@
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/71388177</t>
+          <t>https://artportalen.se/Sighting/71388179</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>54997568</v>
+        <v>71388177</v>
       </c>
       <c r="B45" t="n">
-        <v>58829</v>
+        <v>56833</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5795,47 +5786,53 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100141</v>
+        <v>100111</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mellingeholm, Upl</t>
+          <t>Inventeringslokal 30, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>708179</v>
+        <v>708263</v>
       </c>
       <c r="R45" t="n">
-        <v>6627543</v>
+        <v>6627540</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5860,24 +5857,19 @@
           <t>Frötuna</t>
         </is>
       </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2015-05-15</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>01:15</t>
+          <t>2017-07-14</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2015-05-15</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>01:15</t>
+          <t>2017-07-15</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5892,24 +5884,28 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Daniel Segerlind</t>
+          <t>Gesa von Hirschheydt</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Daniel Segerlind</t>
-        </is>
-      </c>
-      <c r="AY45" t="inlineStr"/>
+          <t>Gesa von Hirschheydt, Lara Millon, Johnny de Jong</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Fladdermöss-Inventering Norrtälje</t>
+        </is>
+      </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54997568</t>
+          <t>https://artportalen.se/Sighting/71388177</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>60067060</v>
+        <v>54997568</v>
       </c>
       <c r="B46" t="n">
         <v>58829</v>
@@ -5939,24 +5935,28 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>hona</t>
-        </is>
-      </c>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Korvsjön Mellingeholm, Upl</t>
+          <t>Mellingeholm, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>708194</v>
+        <v>708179</v>
       </c>
       <c r="R46" t="n">
-        <v>6627547</v>
+        <v>6627543</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5983,22 +5983,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2016-05-24</t>
+          <t>2015-05-15</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>01:15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2016-05-24</t>
+          <t>2015-05-15</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>22:47</t>
+          <t>01:15</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6024,63 +6024,63 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/60067060</t>
+          <t>https://artportalen.se/Sighting/54997568</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>12987878</v>
+        <v>60067060</v>
       </c>
       <c r="B47" t="n">
-        <v>8855</v>
+        <v>58829</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100260</v>
+        <v>100141</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kardinalrödrock</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ampedus cardinalis</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schiödte, 1865)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Mellingeholm Ekbacken, Upl</t>
+          <t>Korvsjön Mellingeholm, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>708078</v>
+        <v>708194</v>
       </c>
       <c r="R47" t="n">
-        <v>6627394</v>
+        <v>6627547</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6104,17 +6104,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2006-05-10</t>
+          <t>2016-05-24</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2006-09-10</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>fönster-/fallfälla</t>
+          <t>2016-05-24</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>22:47</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6126,63 +6131,57 @@
       <c r="AG47" t="b">
         <v>0</v>
       </c>
-      <c r="AQ47" t="inlineStr">
-        <is>
-          <t>Johan Lycke</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr"/>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Johan Lycke</t>
+          <t>Daniel Segerlind</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Johan Lycke</t>
+          <t>Daniel Segerlind</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/12987878</t>
+          <t>https://artportalen.se/Sighting/60067060</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>12987890</v>
+        <v>12987878</v>
       </c>
       <c r="B48" t="n">
-        <v>6269</v>
+        <v>8855</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>101011</v>
+        <v>100260</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Avlång flatbagge</t>
+          <t>Kardinalrödrock</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Grynocharis oblonga</t>
+          <t>Ampedus cardinalis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schiödte, 1865)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -6268,61 +6267,63 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/12987890</t>
+          <t>https://artportalen.se/Sighting/12987878</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134700008</v>
+        <v>12987890</v>
       </c>
       <c r="B49" t="n">
-        <v>8445</v>
+        <v>6269</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>101745</v>
+        <v>101011</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Större apelsplintborre</t>
+          <t>Avlång flatbagge</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Scolytus mali</t>
+          <t>Grynocharis oblonga</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Bechstein &amp; Scharfenberg, 1805)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr">
         <is>
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Mellingeholms herrgårdspark, Upl</t>
+          <t>Mellingeholm Ekbacken, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>708135</v>
+        <v>708078</v>
       </c>
       <c r="R49" t="n">
-        <v>6627412</v>
+        <v>6627394</v>
       </c>
       <c r="S49" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6346,12 +6347,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2006-05-10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2006-09-10</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>fönster-/fallfälla</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6360,53 +6366,39 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>hägg</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Prunus padus</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Prunus padus</t>
-        </is>
-      </c>
+      <c r="AQ49" t="inlineStr">
+        <is>
+          <t>Johan Lycke</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr"/>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Mats Jonsell</t>
+          <t>Johan Lycke</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Mats Jonsell</t>
-        </is>
-      </c>
-      <c r="AY49" t="inlineStr">
-        <is>
-          <t>Svenska entomologmötet i Norrtälje, Uppland 26 - 28 juni 2026</t>
-        </is>
-      </c>
+          <t>Johan Lycke</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134700008</t>
+          <t>https://artportalen.se/Sighting/12987890</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>100482496</v>
+        <v>134700008</v>
       </c>
       <c r="B50" t="n">
-        <v>57942</v>
+        <v>8445</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6414,49 +6406,44 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>102119</v>
+        <v>101745</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Göktyta</t>
+          <t>Större apelsplintborre</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Jynx torquilla</t>
+          <t>Scolytus mali</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
+          <t>(Bechstein &amp; Scharfenberg, 1805)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Melinge holm park, Upl</t>
+          <t>Mellingeholms herrgårdspark, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>708079</v>
+        <v>708135</v>
       </c>
       <c r="R50" t="n">
-        <v>6627430</v>
+        <v>6627412</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6480,22 +6467,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2022-05-04</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>07:30</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2022-05-04</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6504,79 +6481,103 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>hägg</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Prunus padus</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Prunus padus</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Lukas Stenbäck</t>
+          <t>Mats Jonsell</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Lukas Stenbäck</t>
-        </is>
-      </c>
-      <c r="AY50" t="inlineStr"/>
+          <t>Mats Jonsell</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr">
+        <is>
+          <t>Svenska entomologmötet i Norrtälje, Uppland 26 - 28 juni 2026</t>
+        </is>
+      </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100482496</t>
+          <t>https://artportalen.se/Sighting/134700008</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>96897994</v>
+        <v>100482496</v>
       </c>
       <c r="B51" t="n">
-        <v>58592</v>
+        <v>57942</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>102125</v>
+        <v>102119</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tallbit</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pinicola enucleator</t>
+          <t>Jynx torquilla</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mellingeholm f.d slottspark, Upl</t>
+          <t>Melinge holm park, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>708108</v>
+        <v>708079</v>
       </c>
       <c r="R51" t="n">
-        <v>6627395</v>
+        <v>6627430</v>
       </c>
       <c r="S51" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6600,22 +6601,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2022-05-04</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2022-05-04</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6630,27 +6631,27 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll</t>
+          <t>Lukas Stenbäck</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll</t>
+          <t>Lukas Stenbäck</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96897994</t>
+          <t>https://artportalen.se/Sighting/100482496</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>12987917</v>
+        <v>96897994</v>
       </c>
       <c r="B52" t="n">
-        <v>5173</v>
+        <v>58592</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6658,16 +6659,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>102185</v>
+        <v>102125</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Myskbock</t>
+          <t>Tallbit</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Aromia moschata</t>
+          <t>Pinicola enucleator</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6677,27 +6678,26 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Mellingeholm Ekbacken, Upl</t>
+          <t>Mellingeholm f.d slottspark, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>708078</v>
+        <v>708108</v>
       </c>
       <c r="R52" t="n">
-        <v>6627394</v>
+        <v>6627395</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6721,17 +6721,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2006-05-10</t>
+          <t>2021-10-30</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2006-09-10</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>fönsterfälla</t>
+          <t>2021-10-30</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6743,36 +6748,30 @@
       <c r="AG52" t="b">
         <v>0</v>
       </c>
-      <c r="AQ52" t="inlineStr">
-        <is>
-          <t>Johan Lycke</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr"/>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Johan Lycke</t>
+          <t>Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Johan Lycke</t>
+          <t>Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/12987917</t>
+          <t>https://artportalen.se/Sighting/96897994</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134777000</v>
+        <v>12987917</v>
       </c>
       <c r="B53" t="n">
-        <v>45306</v>
+        <v>5173</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6780,21 +6779,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>102918</v>
+        <v>102185</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Citronfläckad kärrtrollslända</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Leucorrhinia pectoralis</t>
+          <t>Aromia moschata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Charpentier, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -6802,36 +6801,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
       <c r="K53" t="inlineStr">
         <is>
           <t>imago/adult</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Mellingeholm, Mellingeholm, Upl</t>
+          <t>Mellingeholm Ekbacken, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>708131</v>
+        <v>708078</v>
       </c>
       <c r="R53" t="n">
-        <v>6627340</v>
+        <v>6627394</v>
       </c>
       <c r="S53" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6855,22 +6842,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>14:48</t>
+          <t>2006-05-10</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>14:48</t>
+          <t>2006-09-10</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>fönsterfälla</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6879,84 +6861,98 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t>Johan Lycke</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr"/>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Elin Gawell</t>
+          <t>Johan Lycke</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Elin Gawell, Niclas Wahlgren</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr">
-        <is>
-          <t>Svenska entomologmötet i Norrtälje, Uppland 26 - 28 juni 2026</t>
-        </is>
-      </c>
+          <t>Johan Lycke</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134777000</t>
+          <t>https://artportalen.se/Sighting/12987917</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>101099374</v>
+        <v>134777000</v>
       </c>
       <c r="B54" t="n">
-        <v>57563</v>
+        <v>45306</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>102966</v>
+        <v>102918</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gråtrut</t>
+          <t>Citronfläckad kärrtrollslända</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Larus argentatus</t>
+          <t>Leucorrhinia pectoralis</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Pontoppidan, 1763</t>
+          <t>(Charpentier, 1825)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Melinge holm park, Upl</t>
+          <t>Mellingeholm, Mellingeholm, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>708079</v>
+        <v>708131</v>
       </c>
       <c r="R54" t="n">
-        <v>6627430</v>
+        <v>6627340</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6980,22 +6976,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7004,33 +7000,38 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Lukas Stenbäck</t>
+          <t>Elin Gawell</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Lukas Stenbäck</t>
-        </is>
-      </c>
-      <c r="AY54" t="inlineStr"/>
+          <t>Elin Gawell, Niclas Wahlgren</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>Svenska entomologmötet i Norrtälje, Uppland 26 - 28 juni 2026</t>
+        </is>
+      </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101099374</t>
+          <t>https://artportalen.se/Sighting/134777000</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>101099371</v>
+        <v>101099374</v>
       </c>
       <c r="B55" t="n">
-        <v>57774</v>
+        <v>57563</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7038,21 +7039,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>102976</v>
+        <v>102966</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Gråtrut</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Larus argentatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pontoppidan, 1763</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -7105,7 +7106,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7115,7 +7116,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>07:52</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7141,43 +7142,43 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101099371</t>
+          <t>https://artportalen.se/Sighting/101099374</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>100259139</v>
+        <v>101099371</v>
       </c>
       <c r="B56" t="n">
-        <v>57947</v>
+        <v>57774</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>102977</v>
+        <v>102976</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -7220,22 +7221,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2022-04-27</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2022-04-27</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7261,13 +7262,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100259139</t>
+          <t>https://artportalen.se/Sighting/101099371</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123359553</v>
+        <v>100259139</v>
       </c>
       <c r="B57" t="n">
         <v>57947</v>
@@ -7302,25 +7303,21 @@
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Melingeholm, Upl</t>
+          <t>Melinge holm park, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>708142</v>
+        <v>708079</v>
       </c>
       <c r="R57" t="n">
-        <v>6627422</v>
+        <v>6627430</v>
       </c>
       <c r="S57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7344,22 +7341,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2022-04-27</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2022-04-27</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7385,16 +7382,16 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123359553</t>
+          <t>https://artportalen.se/Sighting/100259139</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>101099390</v>
+        <v>123359553</v>
       </c>
       <c r="B58" t="n">
-        <v>58420</v>
+        <v>57947</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7402,45 +7399,49 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>102992</v>
+        <v>102977</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Näktergal</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Luscinia luscinia</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Melinge holm park, Upl</t>
+          <t>Melingeholm, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>708079</v>
+        <v>708142</v>
       </c>
       <c r="R58" t="n">
-        <v>6627430</v>
+        <v>6627422</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7464,22 +7465,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7505,13 +7506,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101099390</t>
+          <t>https://artportalen.se/Sighting/123359553</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>101850718</v>
+        <v>101099390</v>
       </c>
       <c r="B59" t="n">
         <v>58420</v>
@@ -7541,7 +7542,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
@@ -7550,17 +7551,17 @@
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>M: Ekpark, Upl</t>
+          <t>Melinge holm park, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>708142</v>
+        <v>708079</v>
       </c>
       <c r="R59" t="n">
-        <v>6627299</v>
+        <v>6627430</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7584,22 +7585,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2022-06-24</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2022-06-24</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7625,66 +7626,62 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101850718</t>
+          <t>https://artportalen.se/Sighting/101099390</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123359526</v>
+        <v>101850718</v>
       </c>
       <c r="B60" t="n">
-        <v>58393</v>
+        <v>58420</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>102999</v>
+        <v>102992</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Näktergal</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Luscinia luscinia</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Melingeholm, Upl</t>
+          <t>M: Ekpark, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
         <v>708142</v>
       </c>
       <c r="R60" t="n">
-        <v>6627422</v>
+        <v>6627299</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7708,22 +7705,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2022-06-24</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2022-06-24</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7749,16 +7746,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123359526</t>
+          <t>https://artportalen.se/Sighting/101850718</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>100676682</v>
+        <v>123359526</v>
       </c>
       <c r="B61" t="n">
-        <v>58179</v>
+        <v>58393</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7766,49 +7763,49 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>103006</v>
+        <v>102999</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rörsångare</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Acrocephalus scirpaceus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hermann, 1804)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="M61" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Melinge holm park, Upl</t>
+          <t>Melingeholm, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>708079</v>
+        <v>708142</v>
       </c>
       <c r="R61" t="n">
-        <v>6627430</v>
+        <v>6627422</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7832,22 +7829,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2022-05-10</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2022-05-10</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7873,16 +7870,16 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100676682</t>
+          <t>https://artportalen.se/Sighting/123359526</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>134700001</v>
+        <v>100676682</v>
       </c>
       <c r="B62" t="n">
-        <v>58201</v>
+        <v>58179</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7912,24 +7909,27 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Mellingeholms herrgårdspark, Upl</t>
+          <t>Melinge holm park, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>708093</v>
+        <v>708079</v>
       </c>
       <c r="R62" t="n">
-        <v>6627431</v>
+        <v>6627430</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7953,22 +7953,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2022-05-10</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2022-05-10</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7983,73 +7983,74 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anders Carlberg</t>
+          <t>Lukas Stenbäck</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anders Carlberg</t>
+          <t>Lukas Stenbäck</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134700001</t>
+          <t>https://artportalen.se/Sighting/100676682</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>101099388</v>
+        <v>134700001</v>
       </c>
       <c r="B63" t="n">
-        <v>58286</v>
+        <v>58201</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103008</v>
+        <v>103006</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Rörsångare</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Acrocephalus scirpaceus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hermann, 1804)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Melinge holm park, Upl</t>
+          <t>Mellingeholms herrgårdspark, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>708079</v>
+        <v>708093</v>
       </c>
       <c r="R63" t="n">
-        <v>6627430</v>
+        <v>6627431</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -8073,22 +8074,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8103,63 +8104,59 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Lukas Stenbäck</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Lukas Stenbäck</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101099388</t>
+          <t>https://artportalen.se/Sighting/134700001</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>100482491</v>
+        <v>101099388</v>
       </c>
       <c r="B64" t="n">
-        <v>58238</v>
+        <v>58286</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>103012</v>
+        <v>103008</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -8197,22 +8194,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2022-05-04</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2022-05-04</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8238,62 +8235,66 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100482491</t>
+          <t>https://artportalen.se/Sighting/101099388</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>96897993</v>
+        <v>100482491</v>
       </c>
       <c r="B65" t="n">
-        <v>58327</v>
+        <v>58238</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>103015</v>
+        <v>103012</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Mellingeholm f.d slottspark, Upl</t>
+          <t>Melinge holm park, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>708108</v>
+        <v>708079</v>
       </c>
       <c r="R65" t="n">
-        <v>6627395</v>
+        <v>6627430</v>
       </c>
       <c r="S65" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8317,22 +8318,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2022-05-04</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2021-10-30</t>
+          <t>2022-05-04</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8347,27 +8348,27 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll</t>
+          <t>Lukas Stenbäck</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll</t>
+          <t>Lukas Stenbäck</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96897993</t>
+          <t>https://artportalen.se/Sighting/100482491</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>100258571</v>
+        <v>96897993</v>
       </c>
       <c r="B66" t="n">
-        <v>58439</v>
+        <v>58327</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8375,53 +8376,45 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Melinge holm park, Upl</t>
+          <t>Mellingeholm f.d slottspark, Upl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>708079</v>
+        <v>708108</v>
       </c>
       <c r="R66" t="n">
-        <v>6627430</v>
+        <v>6627395</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8445,22 +8438,22 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2022-04-27</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2022-04-27</t>
+          <t>2021-10-30</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8475,49 +8468,49 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lukas Stenbäck</t>
+          <t>Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lukas Stenbäck</t>
+          <t>Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100258571</t>
+          <t>https://artportalen.se/Sighting/96897993</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>121950630</v>
+        <v>100258571</v>
       </c>
       <c r="B67" t="n">
-        <v>58114</v>
+        <v>58439</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>103018</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -8526,22 +8519,30 @@
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Melingeholm, Upl</t>
+          <t>Melinge holm park, Upl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>708142</v>
+        <v>708079</v>
       </c>
       <c r="R67" t="n">
-        <v>6627422</v>
+        <v>6627430</v>
       </c>
       <c r="S67" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8565,12 +8566,22 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>2022-04-27</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>07:00</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2025-01-04</t>
+          <t>2022-04-27</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8596,52 +8607,48 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121950630</t>
+          <t>https://artportalen.se/Sighting/100258571</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123359578</v>
+        <v>121950630</v>
       </c>
       <c r="B68" t="n">
-        <v>58353</v>
+        <v>58114</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103037</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
+      <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -8679,22 +8686,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>07:30</t>
+          <t>2025-01-04</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>08:08</t>
+          <t>2025-01-04</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8720,16 +8717,16 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123359578</t>
+          <t>https://artportalen.se/Sighting/121950630</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>101099393</v>
+        <v>123359578</v>
       </c>
       <c r="B69" t="n">
-        <v>58602</v>
+        <v>58353</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8737,45 +8734,49 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103042</v>
+        <v>103037</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Stare</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Sturnus vulgaris</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Melinge holm park, Upl</t>
+          <t>Melingeholm, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>708079</v>
+        <v>708142</v>
       </c>
       <c r="R69" t="n">
-        <v>6627430</v>
+        <v>6627422</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8799,22 +8800,22 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2022-05-24</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8840,33 +8841,33 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101099393</t>
+          <t>https://artportalen.se/Sighting/123359578</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>123359531</v>
+        <v>101099393</v>
       </c>
       <c r="B70" t="n">
-        <v>58636</v>
+        <v>58602</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8874,24 +8875,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Melingeholm, Upl</t>
+          <t>Melinge holm park, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>708142</v>
+        <v>708079</v>
       </c>
       <c r="R70" t="n">
-        <v>6627422</v>
+        <v>6627430</v>
       </c>
       <c r="S70" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8915,22 +8920,22 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2022-05-24</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8956,45 +8961,41 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123359531</t>
+          <t>https://artportalen.se/Sighting/101099393</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>123359444</v>
+        <v>123359531</v>
       </c>
       <c r="B71" t="n">
-        <v>58676</v>
+        <v>58636</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>103055</v>
+        <v>103044</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr"/>
@@ -9076,38 +9077,38 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123359444</t>
+          <t>https://artportalen.se/Sighting/123359531</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>12987817</v>
+        <v>123359444</v>
       </c>
       <c r="B72" t="n">
-        <v>9414</v>
+        <v>58676</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>105076</v>
+        <v>103055</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Noshornsoxe</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Sinodendron cylindricum</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -9115,21 +9116,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Mellingeholm Ekbacken, Upl</t>
+          <t>Melingeholm, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>708078</v>
+        <v>708142</v>
       </c>
       <c r="R72" t="n">
-        <v>6627394</v>
+        <v>6627422</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -9156,17 +9156,22 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2006-05-10</t>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2006-09-10</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>fönsterfälla</t>
+          <t>2025-03-10</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9178,91 +9183,77 @@
       <c r="AG72" t="b">
         <v>0</v>
       </c>
-      <c r="AQ72" t="inlineStr">
-        <is>
-          <t>Johan Lycke</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr"/>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Johan Lycke</t>
+          <t>Lukas Stenbäck</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Johan Lycke</t>
+          <t>Lukas Stenbäck</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/12987817</t>
+          <t>https://artportalen.se/Sighting/123359444</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134792103</v>
+        <v>12987817</v>
       </c>
       <c r="B73" t="n">
-        <v>8374</v>
+        <v>9414</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106540</v>
+        <v>105076</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Noshornsoxe</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Sinodendron cylindricum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Mellingeholms herrgårdspark, Upl</t>
+          <t>Mellingeholm Ekbacken, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>708135</v>
+        <v>708078</v>
       </c>
       <c r="R73" t="n">
-        <v>6627412</v>
+        <v>6627394</v>
       </c>
       <c r="S73" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -9286,12 +9277,17 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2006-05-10</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2006-09-10</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>fönsterfälla</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9300,95 +9296,94 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
+      <c r="AQ73" t="inlineStr">
+        <is>
+          <t>Johan Lycke</t>
+        </is>
+      </c>
+      <c r="AR73" t="inlineStr"/>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Mats Jonsell</t>
+          <t>Johan Lycke</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Mats Jonsell</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr">
-        <is>
-          <t>Svenska entomologmötet i Norrtälje, Uppland 26 - 28 juni 2026</t>
-        </is>
-      </c>
+          <t>Johan Lycke</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134792103</t>
+          <t>https://artportalen.se/Sighting/12987817</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>71388187</v>
+        <v>134792103</v>
       </c>
       <c r="B74" t="n">
-        <v>56823</v>
+        <v>8374</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>205992</v>
+        <v>106540</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>registreringar</t>
-        </is>
-      </c>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>autobox</t>
-        </is>
-      </c>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Inventeringslokal 30, Upl</t>
+          <t>Mellingeholms herrgårdspark, Upl</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>708263</v>
+        <v>708135</v>
       </c>
       <c r="R74" t="n">
-        <v>6627540</v>
+        <v>6627412</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9410,19 +9405,14 @@
           <t>Frötuna</t>
         </is>
       </c>
-      <c r="X74" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2017-07-22</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2017-07-23</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9431,59 +9421,60 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Gesa von Hirschheydt</t>
+          <t>Mats Jonsell</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Gesa von Hirschheydt, Lara Millon, Johnny de Jong</t>
+          <t>Mats Jonsell</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
-          <t>Fladdermöss-Inventering Norrtälje</t>
+          <t>Svenska entomologmötet i Norrtälje, Uppland 26 - 28 juni 2026</t>
         </is>
       </c>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/71388187</t>
+          <t>https://artportalen.se/Sighting/134792103</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>71388176</v>
+        <v>71388187</v>
       </c>
       <c r="B75" t="n">
-        <v>56834</v>
+        <v>56823</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>205994</v>
+        <v>205992</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sydpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pipistrellus pipistrellus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -9547,12 +9538,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2017-07-04</t>
+          <t>2017-07-22</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2017-07-05</t>
+          <t>2017-07-23</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9582,43 +9573,43 @@
       </c>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/71388176</t>
+          <t>https://artportalen.se/Sighting/71388187</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>71388171</v>
+        <v>71388176</v>
       </c>
       <c r="B76" t="n">
-        <v>56835</v>
+        <v>56834</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>205995</v>
+        <v>205994</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Sydpipistrell</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Pipistrellus pipistrellus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -9677,12 +9668,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2017-07-12</t>
+          <t>2017-07-04</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2017-07-13</t>
+          <t>2017-07-05</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9712,43 +9703,43 @@
       </c>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/71388171</t>
+          <t>https://artportalen.se/Sighting/71388176</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>71388190</v>
+        <v>71388171</v>
       </c>
       <c r="B77" t="n">
-        <v>56816</v>
+        <v>56835</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>140</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -9842,68 +9833,70 @@
       </c>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/71388190</t>
+          <t>https://artportalen.se/Sighting/71388171</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>62867864</v>
+        <v>71388190</v>
       </c>
       <c r="B78" t="n">
-        <v>58826</v>
+        <v>56816</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>208242</v>
+        <v>205998</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>larv</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Mellingeholm, Upl</t>
+          <t>Inventeringslokal 30, Upl</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>708179</v>
+        <v>708263</v>
       </c>
       <c r="R78" t="n">
-        <v>6627543</v>
+        <v>6627540</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9928,14 +9921,19 @@
           <t>Frötuna</t>
         </is>
       </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2016-08-18</t>
+          <t>2017-07-12</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2016-08-18</t>
+          <t>2017-07-13</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9950,27 +9948,31 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Daniel Segerlind</t>
+          <t>Gesa von Hirschheydt</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Daniel Segerlind</t>
-        </is>
-      </c>
-      <c r="AY78" t="inlineStr"/>
+          <t>Gesa von Hirschheydt, Lara Millon, Johnny de Jong</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr">
+        <is>
+          <t>Fladdermöss-Inventering Norrtälje</t>
+        </is>
+      </c>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62867864</t>
+          <t>https://artportalen.se/Sighting/71388190</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>59788643</v>
+        <v>62867864</v>
       </c>
       <c r="B79" t="n">
-        <v>58790</v>
+        <v>58826</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9978,16 +9980,16 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>208245</v>
+        <v>208242</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -9995,9 +9997,21 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>larv</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
@@ -10007,10 +10021,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>708222</v>
+        <v>708179</v>
       </c>
       <c r="R79" t="n">
-        <v>6627394</v>
+        <v>6627543</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -10037,12 +10051,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2015-04-27</t>
+          <t>2016-08-18</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2015-04-27</t>
+          <t>2016-08-18</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10068,16 +10082,16 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/59788643</t>
+          <t>https://artportalen.se/Sighting/62867864</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>134738214</v>
+        <v>59788643</v>
       </c>
       <c r="B80" t="n">
-        <v>58812</v>
+        <v>58790</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10110,17 +10124,17 @@
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Gläntan, Upl</t>
+          <t>Mellingeholm, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>708107</v>
+        <v>708222</v>
       </c>
       <c r="R80" t="n">
-        <v>6627443</v>
+        <v>6627394</v>
       </c>
       <c r="S80" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -10144,12 +10158,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2015-04-27</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2015-04-27</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10158,38 +10172,33 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Björn Kallander</t>
+          <t>Daniel Segerlind</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Björn Kallander</t>
-        </is>
-      </c>
-      <c r="AY80" t="inlineStr">
-        <is>
-          <t>Svenska entomologmötet i Norrtälje, Uppland 26 - 28 juni 2026</t>
-        </is>
-      </c>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134738214</t>
+          <t>https://artportalen.se/Sighting/59788643</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>59788573</v>
+        <v>134738214</v>
       </c>
       <c r="B81" t="n">
-        <v>58815</v>
+        <v>58812</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10197,46 +10206,42 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>208250</v>
+        <v>208245</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>äggklumpar</t>
-        </is>
-      </c>
+      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Mellingeholm, Upl</t>
+          <t>Gläntan, Upl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>708179</v>
+        <v>708107</v>
       </c>
       <c r="R81" t="n">
-        <v>6627543</v>
+        <v>6627443</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10260,12 +10265,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2015-04-24</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2015-04-24</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10274,75 +10279,85 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Daniel Segerlind</t>
+          <t>Björn Kallander</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Daniel Segerlind</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr"/>
+          <t>Björn Kallander</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr">
+        <is>
+          <t>Svenska entomologmötet i Norrtälje, Uppland 26 - 28 juni 2026</t>
+        </is>
+      </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/59788573</t>
+          <t>https://artportalen.se/Sighting/134738214</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>110464270</v>
+        <v>59788573</v>
       </c>
       <c r="B82" t="n">
-        <v>106813</v>
+        <v>58815</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220785</v>
+        <v>208250</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>äggklumpar</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Norrtälje kommun, Upl</t>
+          <t>Mellingeholm, Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>708100</v>
+        <v>708179</v>
       </c>
       <c r="R82" t="n">
-        <v>6627383</v>
+        <v>6627543</v>
       </c>
       <c r="S82" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10364,24 +10379,14 @@
           <t>Frötuna</t>
         </is>
       </c>
-      <c r="X82" t="inlineStr">
-        <is>
-          <t>e554aeca-cad2-470c-be2a-1e5e2c625e7f</t>
-        </is>
-      </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>2015-04-24</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>2-delad vid 2m höjd</t>
+          <t>2015-04-24</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10396,28 +10401,24 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Julia Stigenberg</t>
+          <t>Daniel Segerlind</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Miguel Jaramillo</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr">
-        <is>
-          <t>Skyddsvärda träd</t>
-        </is>
-      </c>
+          <t>Daniel Segerlind</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110464270</t>
+          <t>https://artportalen.se/Sighting/59788573</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>110464266</v>
+        <v>110464270</v>
       </c>
       <c r="B83" t="n">
         <v>106813</v>
@@ -10456,10 +10457,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>708178</v>
+        <v>708100</v>
       </c>
       <c r="R83" t="n">
-        <v>6627379</v>
+        <v>6627383</v>
       </c>
       <c r="S83" t="n">
         <v>5</v>
@@ -10486,7 +10487,7 @@
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>521737fd-08ad-43be-95d4-c43615fa6cbb</t>
+          <t>e554aeca-cad2-470c-be2a-1e5e2c625e7f</t>
         </is>
       </c>
       <c r="Y83" t="inlineStr">
@@ -10501,7 +10502,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>2-delad vid 3m höjd</t>
+          <t>2-delad vid 2m höjd</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10531,13 +10532,13 @@
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110464266</t>
+          <t>https://artportalen.se/Sighting/110464270</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>110464234</v>
+        <v>110464266</v>
       </c>
       <c r="B84" t="n">
         <v>106813</v>
@@ -10576,10 +10577,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>708058</v>
+        <v>708178</v>
       </c>
       <c r="R84" t="n">
-        <v>6627352</v>
+        <v>6627379</v>
       </c>
       <c r="S84" t="n">
         <v>5</v>
@@ -10606,7 +10607,7 @@
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>d9f1b0dd-9ab7-4c2b-bc3b-6e06d21224f8</t>
+          <t>521737fd-08ad-43be-95d4-c43615fa6cbb</t>
         </is>
       </c>
       <c r="Y84" t="inlineStr">
@@ -10621,7 +10622,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>4-delad, 2 stammar nedsågade, mätt en stam</t>
+          <t>2-delad vid 3m höjd</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10651,13 +10652,13 @@
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110464234</t>
+          <t>https://artportalen.se/Sighting/110464266</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>83429726</v>
+        <v>110464234</v>
       </c>
       <c r="B85" t="n">
         <v>106813</v>
@@ -10692,17 +10693,17 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>296, 30000321, Upl</t>
+          <t>Norrtälje kommun, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>708145</v>
+        <v>708058</v>
       </c>
       <c r="R85" t="n">
-        <v>6627417</v>
+        <v>6627352</v>
       </c>
       <c r="S85" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10726,17 +10727,22 @@
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>050B5872-D44C-47D4-B13A-E50995FC8704</t>
+          <t>d9f1b0dd-9ab7-4c2b-bc3b-6e06d21224f8</t>
         </is>
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2007-07-24</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2007-07-24</t>
+          <t>2023-04-28</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>4-delad, 2 stammar nedsågade, mätt en stam</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10751,28 +10757,28 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
+          <t>Julia Stigenberg</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
           <t>Miguel Jaramillo</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>Miguel Jaramillo</t>
-        </is>
-      </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t>Trädportalen</t>
+          <t>Skyddsvärda träd</t>
         </is>
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83429726</t>
+          <t>https://artportalen.se/Sighting/110464234</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>110465468</v>
+        <v>83429726</v>
       </c>
       <c r="B86" t="n">
         <v>106813</v>
@@ -10807,17 +10813,17 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Norrtälje kommun, Upl</t>
+          <t>296, 30000321, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>708173</v>
+        <v>708145</v>
       </c>
       <c r="R86" t="n">
-        <v>6627424</v>
+        <v>6627417</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10841,22 +10847,17 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>a0482316-0107-4292-9d58-ec8029e8a662</t>
+          <t>050B5872-D44C-47D4-B13A-E50995FC8704</t>
         </is>
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>2007-07-24</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Hotas av igenväxning.</t>
+          <t>2007-07-24</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10871,7 +10872,7 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Julia Stigenberg</t>
+          <t>Miguel Jaramillo</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
@@ -10881,18 +10882,18 @@
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>Skyddsvärda träd</t>
+          <t>Trädportalen</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110465468</t>
+          <t>https://artportalen.se/Sighting/83429726</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>83431395</v>
+        <v>110465468</v>
       </c>
       <c r="B87" t="n">
         <v>106813</v>
@@ -10927,17 +10928,17 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>296, 30000320, Upl</t>
+          <t>Norrtälje kommun, Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>708122</v>
+        <v>708173</v>
       </c>
       <c r="R87" t="n">
-        <v>6627426</v>
+        <v>6627424</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10961,17 +10962,22 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>698C37A5-1BB1-458D-8873-D68AB5B041CC</t>
+          <t>a0482316-0107-4292-9d58-ec8029e8a662</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2007-07-24</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2007-07-24</t>
+          <t>2023-04-28</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Hotas av igenväxning.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10986,28 +10992,28 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
+          <t>Julia Stigenberg</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
           <t>Miguel Jaramillo</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>Miguel Jaramillo</t>
-        </is>
-      </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>Trädportalen</t>
+          <t>Skyddsvärda träd</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83431395</t>
+          <t>https://artportalen.se/Sighting/110465468</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>110512014</v>
+        <v>83431395</v>
       </c>
       <c r="B88" t="n">
         <v>106813</v>
@@ -11042,17 +11048,17 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Norrtälje kommun, Upl</t>
+          <t>296, 30000320, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>708115</v>
+        <v>708122</v>
       </c>
       <c r="R88" t="n">
-        <v>6627379</v>
+        <v>6627426</v>
       </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -11076,22 +11082,17 @@
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>93f0a388-a771-4d70-b760-01721b10f78e</t>
+          <t>698C37A5-1BB1-458D-8873-D68AB5B041CC</t>
         </is>
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>2007-07-24</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Hotas av igenväxning.</t>
+          <t>2007-07-24</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11106,7 +11107,7 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Julia Stigenberg</t>
+          <t>Miguel Jaramillo</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
@@ -11116,18 +11117,18 @@
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>Skyddsvärda träd</t>
+          <t>Trädportalen</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110512014</t>
+          <t>https://artportalen.se/Sighting/83431395</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>110512011</v>
+        <v>110512014</v>
       </c>
       <c r="B89" t="n">
         <v>106813</v>
@@ -11166,10 +11167,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>707983</v>
+        <v>708115</v>
       </c>
       <c r="R89" t="n">
-        <v>6627132</v>
+        <v>6627379</v>
       </c>
       <c r="S89" t="n">
         <v>5</v>
@@ -11196,7 +11197,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>3afcd3ee-2bc7-4e83-a737-b129de4c8923</t>
+          <t>93f0a388-a771-4d70-b760-01721b10f78e</t>
         </is>
       </c>
       <c r="Y89" t="inlineStr">
@@ -11241,13 +11242,13 @@
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110512011</t>
+          <t>https://artportalen.se/Sighting/110512014</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>83433515</v>
+        <v>110512011</v>
       </c>
       <c r="B90" t="n">
         <v>106813</v>
@@ -11282,17 +11283,17 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>296, 30000311, Upl</t>
+          <t>Norrtälje kommun, Upl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>708068</v>
+        <v>707983</v>
       </c>
       <c r="R90" t="n">
-        <v>6627396</v>
+        <v>6627132</v>
       </c>
       <c r="S90" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11316,17 +11317,22 @@
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>814B74BB-A1E6-421E-BF9A-69FD17385C0F</t>
+          <t>3afcd3ee-2bc7-4e83-a737-b129de4c8923</t>
         </is>
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2007-07-24</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2007-07-24</t>
+          <t>2023-04-28</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Hotas av igenväxning.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11341,28 +11347,28 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
+          <t>Julia Stigenberg</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
           <t>Miguel Jaramillo</t>
         </is>
       </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>Miguel Jaramillo</t>
-        </is>
-      </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>Trädportalen</t>
+          <t>Skyddsvärda träd</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83433515</t>
+          <t>https://artportalen.se/Sighting/110512011</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>110467412</v>
+        <v>83433515</v>
       </c>
       <c r="B91" t="n">
         <v>106813</v>
@@ -11397,17 +11403,17 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Norrtälje kommun, Upl</t>
+          <t>296, 30000311, Upl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>707985</v>
+        <v>708068</v>
       </c>
       <c r="R91" t="n">
-        <v>6627129</v>
+        <v>6627396</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -11431,22 +11437,17 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>65d62958-5b5c-4915-a463-0da62e899892</t>
+          <t>814B74BB-A1E6-421E-BF9A-69FD17385C0F</t>
         </is>
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>2007-07-24</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Hotas av igenväxning.</t>
+          <t>2007-07-24</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11461,7 +11462,7 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Julia Stigenberg</t>
+          <t>Miguel Jaramillo</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
@@ -11471,18 +11472,18 @@
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>Skyddsvärda träd</t>
+          <t>Trädportalen</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110467412</t>
+          <t>https://artportalen.se/Sighting/83433515</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>83434973</v>
+        <v>110467412</v>
       </c>
       <c r="B92" t="n">
         <v>106813</v>
@@ -11517,17 +11518,17 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>300, 30000347, Upl</t>
+          <t>Norrtälje kommun, Upl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>708215</v>
+        <v>707985</v>
       </c>
       <c r="R92" t="n">
-        <v>6627553</v>
+        <v>6627129</v>
       </c>
       <c r="S92" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -11551,17 +11552,22 @@
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>659ACF6F-4E36-42D5-B2D3-418185F5E0FC</t>
+          <t>65d62958-5b5c-4915-a463-0da62e899892</t>
         </is>
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2007-07-25</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2007-07-25</t>
+          <t>2023-04-28</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Hotas av igenväxning.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11576,28 +11582,28 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
+          <t>Julia Stigenberg</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
           <t>Miguel Jaramillo</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>Miguel Jaramillo</t>
-        </is>
-      </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>Trädportalen</t>
+          <t>Skyddsvärda träd</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83434973</t>
+          <t>https://artportalen.se/Sighting/110467412</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>110467416</v>
+        <v>83434973</v>
       </c>
       <c r="B93" t="n">
         <v>106813</v>
@@ -11632,17 +11638,17 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Norrtälje kommun, Upl</t>
+          <t>300, 30000347, Upl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>708188</v>
+        <v>708215</v>
       </c>
       <c r="R93" t="n">
-        <v>6627223</v>
+        <v>6627553</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11666,22 +11672,17 @@
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>c9e54701-ceb6-4c12-bb60-2d648d929522</t>
+          <t>659ACF6F-4E36-42D5-B2D3-418185F5E0FC</t>
         </is>
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>2007-07-25</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Hotas av igenväxning.</t>
+          <t>2007-07-25</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11696,7 +11697,7 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Julia Stigenberg</t>
+          <t>Miguel Jaramillo</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
@@ -11706,18 +11707,18 @@
       </c>
       <c r="AY93" t="inlineStr">
         <is>
-          <t>Skyddsvärda träd</t>
+          <t>Trädportalen</t>
         </is>
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110467416</t>
+          <t>https://artportalen.se/Sighting/83434973</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>110467428</v>
+        <v>110467416</v>
       </c>
       <c r="B94" t="n">
         <v>106813</v>
@@ -11756,10 +11757,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>708099</v>
+        <v>708188</v>
       </c>
       <c r="R94" t="n">
-        <v>6627338</v>
+        <v>6627223</v>
       </c>
       <c r="S94" t="n">
         <v>5</v>
@@ -11786,7 +11787,7 @@
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>927ab8ed-5669-4a45-a069-d9f3875e851b</t>
+          <t>c9e54701-ceb6-4c12-bb60-2d648d929522</t>
         </is>
       </c>
       <c r="Y94" t="inlineStr">
@@ -11831,13 +11832,13 @@
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110467428</t>
+          <t>https://artportalen.se/Sighting/110467416</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>110467409</v>
+        <v>110467428</v>
       </c>
       <c r="B95" t="n">
         <v>106813</v>
@@ -11876,10 +11877,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>708215</v>
+        <v>708099</v>
       </c>
       <c r="R95" t="n">
-        <v>6627554</v>
+        <v>6627338</v>
       </c>
       <c r="S95" t="n">
         <v>5</v>
@@ -11906,7 +11907,7 @@
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>543b97f9-cae8-427d-a498-c19c6a88aa76</t>
+          <t>927ab8ed-5669-4a45-a069-d9f3875e851b</t>
         </is>
       </c>
       <c r="Y95" t="inlineStr">
@@ -11951,13 +11952,13 @@
       </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110467409</t>
+          <t>https://artportalen.se/Sighting/110467428</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>110467423</v>
+        <v>110467409</v>
       </c>
       <c r="B96" t="n">
         <v>106813</v>
@@ -11996,10 +11997,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>708068</v>
+        <v>708215</v>
       </c>
       <c r="R96" t="n">
-        <v>6627395</v>
+        <v>6627554</v>
       </c>
       <c r="S96" t="n">
         <v>5</v>
@@ -12026,7 +12027,7 @@
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>05253557-5e81-4ede-847c-695cd3ed5e3c</t>
+          <t>543b97f9-cae8-427d-a498-c19c6a88aa76</t>
         </is>
       </c>
       <c r="Y96" t="inlineStr">
@@ -12071,13 +12072,13 @@
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110467423</t>
+          <t>https://artportalen.se/Sighting/110467409</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>110512016</v>
+        <v>110467423</v>
       </c>
       <c r="B97" t="n">
         <v>106813</v>
@@ -12116,10 +12117,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>708146</v>
+        <v>708068</v>
       </c>
       <c r="R97" t="n">
-        <v>6627417</v>
+        <v>6627395</v>
       </c>
       <c r="S97" t="n">
         <v>5</v>
@@ -12146,7 +12147,7 @@
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>eadfe9b1-3d31-4f5c-a1f8-fe8ad5c91243</t>
+          <t>05253557-5e81-4ede-847c-695cd3ed5e3c</t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
@@ -12191,13 +12192,13 @@
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110512016</t>
+          <t>https://artportalen.se/Sighting/110467423</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>110512018</v>
+        <v>110512016</v>
       </c>
       <c r="B98" t="n">
         <v>106813</v>
@@ -12236,10 +12237,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>708121</v>
+        <v>708146</v>
       </c>
       <c r="R98" t="n">
-        <v>6627426</v>
+        <v>6627417</v>
       </c>
       <c r="S98" t="n">
         <v>5</v>
@@ -12266,7 +12267,7 @@
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>b48b1242-968c-46ff-a639-929c113541ab</t>
+          <t>eadfe9b1-3d31-4f5c-a1f8-fe8ad5c91243</t>
         </is>
       </c>
       <c r="Y98" t="inlineStr">
@@ -12311,33 +12312,33 @@
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110512018</t>
+          <t>https://artportalen.se/Sighting/110512016</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>77423734</v>
+        <v>110512018</v>
       </c>
       <c r="B99" t="n">
-        <v>106156</v>
+        <v>106813</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221141</v>
+        <v>220785</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -12345,24 +12346,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Holmen, Frötuna, Upl</t>
+          <t>Norrtälje kommun, Upl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>708459</v>
+        <v>708121</v>
       </c>
       <c r="R99" t="n">
-        <v>6627423</v>
+        <v>6627426</v>
       </c>
       <c r="S99" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -12384,14 +12385,24 @@
           <t>Frötuna</t>
         </is>
       </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>b48b1242-968c-46ff-a639-929c113541ab</t>
+        </is>
+      </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2019-04-30</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2019-04-30</t>
+          <t>2023-04-28</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Hotas av igenväxning.</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12400,34 +12411,37 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Josefin Sundberg</t>
+          <t>Julia Stigenberg</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Josefin Sundberg</t>
-        </is>
-      </c>
-      <c r="AY99" t="inlineStr"/>
+          <t>Miguel Jaramillo</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/77423734</t>
+          <t>https://artportalen.se/Sighting/110512018</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>109247157</v>
+        <v>77423734</v>
       </c>
       <c r="B100" t="n">
-        <v>101326</v>
+        <v>106156</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12435,35 +12449,38 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Vrangsmon, Upl</t>
+          <t>Holmen, Frötuna, Upl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>707942</v>
+        <v>708459</v>
       </c>
       <c r="R100" t="n">
-        <v>6627081</v>
+        <v>6627423</v>
       </c>
       <c r="S100" t="n">
         <v>25</v>
@@ -12490,22 +12507,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
-        </is>
-      </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>19:36</t>
+          <t>2019-04-30</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2023-05-17</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>19:36</t>
+          <t>2019-04-30</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12514,33 +12521,34 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Josefin Sundberg</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Josefin Sundberg</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109247157</t>
+          <t>https://artportalen.se/Sighting/77423734</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>69549718</v>
+        <v>109247157</v>
       </c>
       <c r="B101" t="n">
-        <v>101159</v>
+        <v>101326</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12548,37 +12556,38 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>222817</v>
+        <v>222498</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Smånunneört</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Corydalis intermedia</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Mérat</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Holmen, SO om Görla, Upl</t>
+          <t>Vrangsmon, Upl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>708410</v>
+        <v>707942</v>
       </c>
       <c r="R101" t="n">
-        <v>6627454</v>
+        <v>6627081</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -12602,17 +12611,22 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2023-05-17</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>19:36</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2004-12-31</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Upplandsfloran - detaljuppgifter.</t>
+          <t>2023-05-17</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>19:36</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12623,40 +12637,31 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
-      </c>
-      <c r="AI101" t="inlineStr">
-        <is>
-          <t>Lund</t>
-        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Mora Aronsson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
-        </is>
-      </c>
-      <c r="AY101" t="inlineStr">
-        <is>
-          <t>Upplands Flora 2010</t>
-        </is>
-      </c>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/69549718</t>
+          <t>https://artportalen.se/Sighting/109247157</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118335499</v>
+        <v>69549718</v>
       </c>
       <c r="B102" t="n">
-        <v>89060</v>
+        <v>101159</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12664,25 +12669,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>239221</v>
+        <v>222817</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Smånunneört</t>
+        </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Gliophorus psittacinus var. psittacinus</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr"/>
+          <t>Corydalis intermedia</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(L.) Mérat</t>
+        </is>
+      </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Mellingeholm, Mellingeholm, Upl</t>
+          <t>Holmen, SO om Görla, Upl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>708181</v>
+        <v>708410</v>
       </c>
       <c r="R102" t="n">
-        <v>6627281</v>
+        <v>6627454</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12709,27 +12723,17 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2023-07-28</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2004-12-31</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Kollekt 4155.</t>
+          <t>Upplandsfloran - detaljuppgifter.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12740,26 +12744,31 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>Lund</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Mora Aronsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>Svampar i Roslagen</t>
+          <t>Upplands Flora 2010</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118335499</t>
+          <t>https://artportalen.se/Sighting/69549718</t>
         </is>
       </c>
     </row>

--- a/artfynd/S 5521-2022 artfynd.xlsx
+++ b/artfynd/S 5521-2022 artfynd.xlsx
@@ -3627,7 +3627,7 @@
         <v>118335499</v>
       </c>
       <c r="B27" t="n">
-        <v>89206</v>
+        <v>89207</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/S 5521-2022 artfynd.xlsx
+++ b/artfynd/S 5521-2022 artfynd.xlsx
@@ -3627,7 +3627,7 @@
         <v>118335499</v>
       </c>
       <c r="B27" t="n">
-        <v>89207</v>
+        <v>89213</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/S 5521-2022 artfynd.xlsx
+++ b/artfynd/S 5521-2022 artfynd.xlsx
@@ -3627,7 +3627,7 @@
         <v>118335499</v>
       </c>
       <c r="B27" t="n">
-        <v>89213</v>
+        <v>89220</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/S 5521-2022 artfynd.xlsx
+++ b/artfynd/S 5521-2022 artfynd.xlsx
@@ -3627,7 +3627,7 @@
         <v>118335499</v>
       </c>
       <c r="B27" t="n">
-        <v>89220</v>
+        <v>89221</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/S 5521-2022 artfynd.xlsx
+++ b/artfynd/S 5521-2022 artfynd.xlsx
@@ -3627,7 +3627,7 @@
         <v>118335499</v>
       </c>
       <c r="B27" t="n">
-        <v>89221</v>
+        <v>89234</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/S 5521-2022 artfynd.xlsx
+++ b/artfynd/S 5521-2022 artfynd.xlsx
@@ -3627,7 +3627,7 @@
         <v>118335499</v>
       </c>
       <c r="B27" t="n">
-        <v>89234</v>
+        <v>89235</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
